--- a/docs/progress/TopoGym_环境进度追踪表.xlsx
+++ b/docs/progress/TopoGym_环境进度追踪表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luigi\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\NWU-Y2\CS499\topogym\topogym\docs\progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93294684-3E6A-4DC3-AACD-DEC3FFAC1370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD61B17-97A1-4141-853B-D1D5E2AE2441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -690,12 +690,6 @@
   </cellStyleXfs>
   <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -746,6 +740,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1061,474 +1061,474 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.75" customHeight="1">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="32.25" customHeight="1">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" s="8" t="s">
+      <c r="F2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="8" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="8" t="s">
+      <c r="C4" s="18"/>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="32.25" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="8" t="s">
+      <c r="C5" s="18"/>
+      <c r="D5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H6" s="8" t="s">
+      <c r="C6" s="18"/>
+      <c r="D6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="8"/>
+      <c r="D7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="7" t="s">
+      <c r="C8" s="18"/>
+      <c r="D8" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="8"/>
+      <c r="F8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" ht="63.75" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="7" t="s">
+      <c r="C9" s="18"/>
+      <c r="D9" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="F9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="7" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="C10" s="18"/>
+      <c r="D10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H11" s="9"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="7"/>
     </row>
     <row r="12" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="9"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="7"/>
     </row>
     <row r="13" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H13" s="9"/>
+      <c r="F13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="7"/>
     </row>
     <row r="14" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="9"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="7"/>
     </row>
     <row r="15" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H15" s="9"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="7"/>
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H16" s="9"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="8" t="s">
+      <c r="F17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="32.25" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H18" s="9"/>
+      <c r="F18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="1:8" ht="63.75" customHeight="1">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="7" t="s">
+      <c r="C19" s="18"/>
+      <c r="D19" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H19" s="8" t="s">
+      <c r="F19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="7" t="s">
+      <c r="C20" s="18"/>
+      <c r="D20" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="9"/>
+      <c r="F20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1572,226 +1572,226 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.6">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="5" spans="1:6" ht="15.6">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="9" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
     </row>
     <row r="11" spans="1:6" ht="15.6">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
+      <c r="A12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="16" spans="1:6" ht="15.6">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="10" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="17" t="s">
-        <v>11</v>
-      </c>
-      <c r="B18" s="18">
+      <c r="A18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="16">
         <f>COUNTIF(进度追踪!D$2:D$20,$A18)</f>
-        <v>11</v>
-      </c>
-      <c r="C18" s="18">
+        <v>9</v>
+      </c>
+      <c r="C18" s="16">
         <f>COUNTIF(进度追踪!E$2:E$20,$A18)</f>
-        <v>11</v>
-      </c>
-      <c r="D18" s="18">
+        <v>9</v>
+      </c>
+      <c r="D18" s="16">
         <f>COUNTIF(进度追踪!F$2:F$20,$A18)</f>
         <v>19</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="16">
         <f>COUNTIF(进度追踪!G$2:G$20,$A18)</f>
         <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="16">
         <f>COUNTIF(进度追踪!D$2:D$20,$A19)</f>
-        <v>1</v>
-      </c>
-      <c r="C19" s="18">
+        <v>2</v>
+      </c>
+      <c r="C19" s="16">
         <f>COUNTIF(进度追踪!E$2:E$20,$A19)</f>
-        <v>5</v>
-      </c>
-      <c r="D19" s="18">
+        <v>7</v>
+      </c>
+      <c r="D19" s="16">
         <f>COUNTIF(进度追踪!F$2:F$20,$A19)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="16">
         <f>COUNTIF(进度追踪!G$2:G$20,$A19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="16">
         <f>COUNTIF(进度追踪!D$2:D$20,$A20)</f>
-        <v>7</v>
-      </c>
-      <c r="C20" s="18">
+        <v>8</v>
+      </c>
+      <c r="C20" s="16">
         <f>COUNTIF(进度追踪!E$2:E$20,$A20)</f>
         <v>3</v>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="16">
         <f>COUNTIF(进度追踪!F$2:F$20,$A20)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="16">
         <f>COUNTIF(进度追踪!G$2:G$20,$A20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="12" t="s">
+      <c r="A21" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B21" s="19">
+      <c r="B21" s="17">
         <f>SUM(B18:B20)</f>
         <v>19</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="17">
         <f>SUM(C18:C20)</f>
         <v>19</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="17">
         <f>SUM(D18:D20)</f>
         <v>19</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="17">
         <f>SUM(E18:E20)</f>
         <v>19</v>
       </c>

--- a/docs/progress/TopoGym_环境进度追踪表.xlsx
+++ b/docs/progress/TopoGym_环境进度追踪表.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">

--- a/docs/progress/TopoGym_环境进度追踪表.xlsx
+++ b/docs/progress/TopoGym_环境进度追踪表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\NWU-Y2\CS499\topogym\topogym\docs\progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DD61B17-97A1-4141-853B-D1D5E2AE2441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D4D1BF-5539-4E81-B425-5D4BF18449CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1121,10 +1121,10 @@
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="5" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>11</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="5" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>11</v>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="5" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>11</v>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="5" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>11</v>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>69</v>
@@ -1718,11 +1718,11 @@
       </c>
       <c r="B18" s="16">
         <f>COUNTIF(进度追踪!D$2:D$20,$A18)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C18" s="16">
         <f>COUNTIF(进度追踪!E$2:E$20,$A18)</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="16">
         <f>COUNTIF(进度追踪!F$2:F$20,$A18)</f>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="B19" s="16">
         <f>COUNTIF(进度追踪!D$2:D$20,$A19)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C19" s="16">
         <f>COUNTIF(进度追踪!E$2:E$20,$A19)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="16">
         <f>COUNTIF(进度追踪!F$2:F$20,$A19)</f>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="B20" s="16">
         <f>COUNTIF(进度追踪!D$2:D$20,$A20)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" s="16">
         <f>COUNTIF(进度追踪!E$2:E$20,$A20)</f>

--- a/docs/progress/TopoGym_环境进度追踪表.xlsx
+++ b/docs/progress/TopoGym_环境进度追踪表.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D4D1BF-5539-4E81-B425-5D4BF18449CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="进度追踪" sheetId="1" r:id="rId1"/>

--- a/docs/progress/TopoGym_环境进度追踪表.xlsx
+++ b/docs/progress/TopoGym_环境进度追踪表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\NWU-Y2\CS499\topogym\topogym\docs\progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D4D1BF-5539-4E81-B425-5D4BF18449CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966F0AA7-A020-4030-B18D-461DDADB84CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -266,21 +266,70 @@
     <t>3.3</t>
   </si>
   <si>
+    <t>3.4</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">8 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">字绳圈改成 </t>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>形环从固定圆环中解开</t>
+    </r>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>关闭挡板困住移动小球</t>
+  </si>
+  <si>
+    <t>连接与可达性</t>
+  </si>
+  <si>
+    <t>前置参数扫描（球速等）会议确认有必要进行</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>对齐圆盘缺口让杆子进入（stacked plate）</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>旋转分流板改变小球出口</t>
+  </si>
+  <si>
+    <t>会议确定的场景修改：封闭左侧通道并延长、添加红色目标标记；分流板辨识度低，需改进几何表达或更换资产（现实参考：《3D 平衡球》）；旋转角度不足会导致球卡住，需纳入设计；场景修改后 planner 需复核</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>旋转连接杆合并两个组件</t>
+  </si>
+  <si>
+    <t>使用说明</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">需要编辑的单元格：进度追踪表 </t>
     </r>
     <r>
       <rPr>
@@ -288,82 +337,31 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">O </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>形（解半扭转）</t>
-    </r>
-  </si>
-  <si>
-    <t>3.4</t>
-  </si>
-  <si>
+      <t xml:space="preserve">D–G </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列的状态（下拉选择）与 </t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">C </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>形环从固定圆环中解开</t>
-    </r>
-  </si>
-  <si>
-    <t>4.1</t>
-  </si>
-  <si>
-    <t>关闭挡板困住移动小球</t>
-  </si>
-  <si>
-    <t>连接与可达性</t>
-  </si>
-  <si>
-    <t>前置参数扫描（球速等）会议确认有必要进行</t>
-  </si>
-  <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>对齐圆盘缺口让杆子进入（stacked plate）</t>
-  </si>
-  <si>
-    <t>4.3</t>
-  </si>
-  <si>
-    <t>旋转分流板改变小球出口</t>
-  </si>
-  <si>
-    <t>会议确定的场景修改：封闭左侧通道并延长、添加红色目标标记；分流板辨识度低，需改进几何表达或更换资产（现实参考：《3D 平衡球》）；旋转角度不足会导致球卡住，需纳入设计；场景修改后 planner 需复核</t>
-  </si>
-  <si>
-    <t>4.4</t>
-  </si>
-  <si>
-    <t>旋转连接杆合并两个组件</t>
-  </si>
-  <si>
-    <t>使用说明</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">需要编辑的单元格：进度追踪表 </t>
+      <t xml:space="preserve">H </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">列备注。其余列为任务信息，来源为 </t>
     </r>
     <r>
       <rPr>
@@ -371,15 +369,25 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">D–G </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列的状态（下拉选择）与 </t>
+      <t xml:space="preserve">TopoGym </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>任务文档。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">状态初始值统一为未开始，由本人逐项填写更新。备注列保留了 </t>
     </r>
     <r>
       <rPr>
@@ -387,15 +395,34 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">H </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">列备注。其余列为任务信息，来源为 </t>
+      <t xml:space="preserve">2026-08-19 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>会议中与各任务相关的记录，供填写时参考。</t>
+    </r>
+  </si>
+  <si>
+    <t>里程碑定义</t>
+  </si>
+  <si>
+    <t>场景搭建与相机配置（腕部相机与第三人称视角相机）全部调好</t>
+  </si>
+  <si>
+    <t>对任意给定状态输出标准动作序列的求解器</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>域随机化变体的参数轴设定，以及对应的场景变体生成器（</t>
     </r>
     <r>
       <rPr>
@@ -403,60 +430,45 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">TopoGym </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>任务文档。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">状态初始值统一为未开始，由本人逐项填写更新。备注列保留了 </t>
-    </r>
-    <r>
-      <rPr>
+      <t>generator</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">生成数据 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
         <sz val="11"/>
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2026-08-19 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>会议中与各任务相关的记录，供填写时参考。</t>
-    </r>
-  </si>
-  <si>
-    <t>里程碑定义</t>
-  </si>
-  <si>
-    <t>场景搭建与相机配置（腕部相机与第三人称视角相机）全部调好</t>
-  </si>
-  <si>
-    <t>对任意给定状态输出标准动作序列的求解器</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>域随机化变体的参数轴设定，以及对应的场景变体生成器（</t>
+      <t>Pipeline</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">由 </t>
     </r>
     <r>
       <rPr>
@@ -464,96 +476,82 @@
         <rFont val="Arial"/>
         <charset val="1"/>
       </rPr>
-      <t>generator</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">生成数据 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
+      <t xml:space="preserve">Oracle Planner </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>批量生成模仿学习数据的流水线（含渲染与存储）</t>
+    </r>
+  </si>
+  <si>
+    <t>状态取值</t>
+  </si>
+  <si>
+    <t>该里程碑尚未开始</t>
+  </si>
+  <si>
+    <t>进行中</t>
+  </si>
+  <si>
+    <t>该里程碑存在未完成事项，正在处理</t>
+  </si>
+  <si>
+    <t>已完成</t>
+  </si>
+  <si>
+    <t>该里程碑已完成</t>
+  </si>
+  <si>
+    <t>汇总统计（随进度追踪表自动更新）</t>
+  </si>
+  <si>
+    <t>状态</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">字绳圈改成 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
         <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Pipeline</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">由 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Arial"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Oracle Planner </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>批量生成模仿学习数据的流水线（含渲染与存储）</t>
-    </r>
-  </si>
-  <si>
-    <t>状态取值</t>
-  </si>
-  <si>
-    <t>该里程碑尚未开始</t>
-  </si>
-  <si>
-    <t>进行中</t>
-  </si>
-  <si>
-    <t>该里程碑存在未完成事项，正在处理</t>
-  </si>
-  <si>
-    <t>已完成</t>
-  </si>
-  <si>
-    <t>该里程碑已完成</t>
-  </si>
-  <si>
-    <t>汇总统计（随进度追踪表自动更新）</t>
-  </si>
-  <si>
-    <t>状态</t>
-  </si>
-  <si>
-    <t>合计</t>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">O </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t>形（解半扭转）</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -628,6 +626,25 @@
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -688,7 +705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -746,6 +763,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1097,10 +1120,10 @@
         <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>11</v>
@@ -1121,10 +1144,10 @@
       </c>
       <c r="C3" s="18"/>
       <c r="D3" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>11</v>
@@ -1145,7 +1168,7 @@
       </c>
       <c r="C4" s="18"/>
       <c r="D4" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>11</v>
@@ -1169,7 +1192,7 @@
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>11</v>
@@ -1188,7 +1211,7 @@
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="20" t="s">
         <v>22</v>
       </c>
       <c r="C6" s="18"/>
@@ -1212,7 +1235,7 @@
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="20" t="s">
         <v>24</v>
       </c>
       <c r="C7" s="18" t="s">
@@ -1241,10 +1264,10 @@
       </c>
       <c r="C8" s="18"/>
       <c r="D8" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>11</v>
@@ -1263,10 +1286,10 @@
       </c>
       <c r="C9" s="18"/>
       <c r="D9" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>11</v>
@@ -1282,7 +1305,7 @@
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="20" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="18"/>
@@ -1311,7 +1334,7 @@
       </c>
       <c r="C11" s="18"/>
       <c r="D11" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="5" t="s">
         <v>11</v>
@@ -1357,10 +1380,10 @@
         <v>40</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>11</v>
@@ -1379,10 +1402,10 @@
       </c>
       <c r="C14" s="18"/>
       <c r="D14" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>11</v>
@@ -1396,8 +1419,8 @@
       <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>44</v>
+      <c r="B15" s="21" t="s">
+        <v>75</v>
       </c>
       <c r="C15" s="18"/>
       <c r="D15" s="5" t="s">
@@ -1416,17 +1439,17 @@
     </row>
     <row r="16" spans="1:8" ht="16.5" customHeight="1">
       <c r="A16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>45</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>46</v>
       </c>
       <c r="C16" s="18"/>
       <c r="D16" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>11</v>
@@ -1438,43 +1461,43 @@
     </row>
     <row r="17" spans="1:8" ht="16.5" customHeight="1">
       <c r="A17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="C17" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="D17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>49</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="32.25" customHeight="1">
       <c r="A18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="C18" s="18"/>
       <c r="D18" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>11</v>
@@ -1486,17 +1509,17 @@
     </row>
     <row r="19" spans="1:8" ht="63.75" customHeight="1">
       <c r="A19" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>54</v>
       </c>
       <c r="C19" s="18"/>
       <c r="D19" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>11</v>
@@ -1505,22 +1528,22 @@
         <v>11</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="16.5" customHeight="1">
       <c r="A20" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>57</v>
       </c>
       <c r="C20" s="18"/>
       <c r="D20" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>11</v>
@@ -1573,12 +1596,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15.6">
       <c r="A1" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A2" s="19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" s="19"/>
       <c r="C2" s="19"/>
@@ -1588,7 +1611,7 @@
     </row>
     <row r="3" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A3" s="19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -1598,7 +1621,7 @@
     </row>
     <row r="5" spans="1:6" ht="15.6">
       <c r="A5" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="17.100000000000001" customHeight="1">
@@ -1606,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C6" s="19"/>
       <c r="D6" s="19"/>
@@ -1618,7 +1641,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="19"/>
       <c r="D7" s="19"/>
@@ -1630,7 +1653,7 @@
         <v>5</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19"/>
@@ -1639,10 +1662,10 @@
     </row>
     <row r="9" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A9" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>65</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>66</v>
       </c>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -1651,7 +1674,7 @@
     </row>
     <row r="11" spans="1:6" ht="15.6">
       <c r="A11" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="17.100000000000001" customHeight="1">
@@ -1659,7 +1682,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C12" s="19"/>
       <c r="D12" s="19"/>
@@ -1668,10 +1691,10 @@
     </row>
     <row r="13" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>69</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>70</v>
       </c>
       <c r="C13" s="19"/>
       <c r="D13" s="19"/>
@@ -1680,10 +1703,10 @@
     </row>
     <row r="14" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A14" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>71</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>72</v>
       </c>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -1692,12 +1715,12 @@
     </row>
     <row r="16" spans="1:6" ht="15.6">
       <c r="A16" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>3</v>
@@ -1709,7 +1732,7 @@
         <v>5</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1735,7 +1758,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B19" s="16">
         <f>COUNTIF(进度追踪!D$2:D$20,$A19)</f>
@@ -1756,7 +1779,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B20" s="16">
         <f>COUNTIF(进度追踪!D$2:D$20,$A20)</f>
@@ -1777,7 +1800,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="17">
         <f>SUM(B18:B20)</f>

--- a/docs/progress/TopoGym_环境进度追踪表.xlsx
+++ b/docs/progress/TopoGym_环境进度追踪表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\NWU-Y2\CS499\topogym\topogym\docs\progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{966F0AA7-A020-4030-B18D-461DDADB84CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D602BAA-1343-4582-836C-114B86A9428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -758,17 +758,17 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1116,7 +1116,7 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="20" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1142,7 +1142,7 @@
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="18"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="5" t="s">
         <v>70</v>
       </c>
@@ -1166,7 +1166,7 @@
       <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="18"/>
+      <c r="C4" s="20"/>
       <c r="D4" s="5" t="s">
         <v>68</v>
       </c>
@@ -1190,7 +1190,7 @@
       <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="18"/>
+      <c r="C5" s="20"/>
       <c r="D5" s="5" t="s">
         <v>68</v>
       </c>
@@ -1211,10 +1211,10 @@
       <c r="A6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="18"/>
+      <c r="C6" s="20"/>
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
@@ -1235,10 +1235,10 @@
       <c r="A7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="20" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1262,7 +1262,7 @@
       <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="18"/>
+      <c r="C8" s="20"/>
       <c r="D8" s="5" t="s">
         <v>70</v>
       </c>
@@ -1284,7 +1284,7 @@
       <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="18"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="5" t="s">
         <v>70</v>
       </c>
@@ -1305,10 +1305,10 @@
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="18"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="5" t="s">
         <v>11</v>
       </c>
@@ -1332,7 +1332,7 @@
       <c r="B11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="18"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="5" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1354,7 @@
       <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="18"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1376,7 +1376,7 @@
       <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="20" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1400,7 +1400,7 @@
       <c r="B14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="18"/>
+      <c r="C14" s="20"/>
       <c r="D14" s="5" t="s">
         <v>70</v>
       </c>
@@ -1419,10 +1419,10 @@
       <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="18"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1444,7 +1444,7 @@
       <c r="B16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="18"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="5" t="s">
         <v>70</v>
       </c>
@@ -1466,7 +1466,7 @@
       <c r="B17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="20" t="s">
         <v>48</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -1492,7 +1492,7 @@
       <c r="B18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="18"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="5" t="s">
         <v>70</v>
       </c>
@@ -1514,7 +1514,7 @@
       <c r="B19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="18"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="5" t="s">
         <v>70</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="B20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="18"/>
+      <c r="C20" s="20"/>
       <c r="D20" s="5" t="s">
         <v>68</v>
       </c>
@@ -1600,24 +1600,24 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
+      <c r="B3" s="21"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="5" spans="1:6" ht="15.6">
       <c r="A5" s="9" t="s">
@@ -1628,49 +1628,49 @@
       <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="7" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A7" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="11" spans="1:6" ht="15.6">
       <c r="A11" s="9" t="s">
@@ -1681,37 +1681,37 @@
       <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A14" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="16" spans="1:6" ht="15.6">
       <c r="A16" s="9" t="s">

--- a/docs/progress/TopoGym_环境进度追踪表.xlsx
+++ b/docs/progress/TopoGym_环境进度追踪表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\E\NWU-Y2\CS499\topogym\topogym\docs\progress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D602BAA-1343-4582-836C-114B86A9428B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F18BB55A-9BC5-413A-8BDC-EB45005D251B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="2232" windowWidth="17280" windowHeight="8880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="进度追踪" sheetId="1" r:id="rId1"/>
@@ -521,7 +521,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFFC000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -530,7 +530,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFFC000"/>
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
@@ -539,7 +539,7 @@
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFFC000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -551,7 +551,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -635,13 +635,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFC000"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFC000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFC000"/>
       <name val="Noto Sans CJK SC"/>
       <family val="2"/>
     </font>
@@ -705,7 +712,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -761,14 +768,17 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1116,7 +1126,7 @@
       <c r="B2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="5" t="s">
@@ -1142,7 +1152,7 @@
       <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="19"/>
       <c r="D3" s="5" t="s">
         <v>70</v>
       </c>
@@ -1166,7 +1176,7 @@
       <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="20"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="5" t="s">
         <v>68</v>
       </c>
@@ -1187,10 +1197,10 @@
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="20"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="5" t="s">
         <v>68</v>
       </c>
@@ -1214,7 +1224,7 @@
       <c r="B6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="20"/>
+      <c r="C6" s="19"/>
       <c r="D6" s="5" t="s">
         <v>11</v>
       </c>
@@ -1238,7 +1248,7 @@
       <c r="B7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>25</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1262,7 +1272,7 @@
       <c r="B8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="20"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="5" t="s">
         <v>70</v>
       </c>
@@ -1284,7 +1294,7 @@
       <c r="B9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="20"/>
+      <c r="C9" s="19"/>
       <c r="D9" s="5" t="s">
         <v>70</v>
       </c>
@@ -1305,10 +1315,10 @@
       <c r="A10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="20"/>
+      <c r="C10" s="19"/>
       <c r="D10" s="5" t="s">
         <v>11</v>
       </c>
@@ -1332,7 +1342,7 @@
       <c r="B11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="20"/>
+      <c r="C11" s="19"/>
       <c r="D11" s="5" t="s">
         <v>68</v>
       </c>
@@ -1354,7 +1364,7 @@
       <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="20"/>
+      <c r="C12" s="19"/>
       <c r="D12" s="5" t="s">
         <v>11</v>
       </c>
@@ -1376,7 +1386,7 @@
       <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="5" t="s">
@@ -1400,7 +1410,7 @@
       <c r="B14" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="20"/>
+      <c r="C14" s="19"/>
       <c r="D14" s="5" t="s">
         <v>70</v>
       </c>
@@ -1419,10 +1429,10 @@
       <c r="A15" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="20"/>
+      <c r="C15" s="19"/>
       <c r="D15" s="5" t="s">
         <v>11</v>
       </c>
@@ -1444,7 +1454,7 @@
       <c r="B16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="20"/>
+      <c r="C16" s="19"/>
       <c r="D16" s="5" t="s">
         <v>70</v>
       </c>
@@ -1466,7 +1476,7 @@
       <c r="B17" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="20" t="s">
+      <c r="C17" s="19" t="s">
         <v>48</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -1492,7 +1502,7 @@
       <c r="B18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="20"/>
+      <c r="C18" s="19"/>
       <c r="D18" s="5" t="s">
         <v>70</v>
       </c>
@@ -1514,7 +1524,7 @@
       <c r="B19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="20"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="5" t="s">
         <v>70</v>
       </c>
@@ -1538,7 +1548,7 @@
       <c r="B20" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C20" s="20"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="5" t="s">
         <v>68</v>
       </c>
@@ -1600,24 +1610,24 @@
       </c>
     </row>
     <row r="2" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
     </row>
     <row r="3" spans="1:6" ht="17.100000000000001" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="20" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
     </row>
     <row r="5" spans="1:6" ht="15.6">
       <c r="A5" s="9" t="s">
@@ -1628,49 +1638,49 @@
       <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C6" s="21"/>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-      <c r="F6" s="21"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
     </row>
     <row r="7" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A7" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="21"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
+      <c r="F7" s="20"/>
     </row>
     <row r="8" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
     </row>
     <row r="9" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
     </row>
     <row r="11" spans="1:6" ht="15.6">
       <c r="A11" s="9" t="s">
@@ -1681,37 +1691,37 @@
       <c r="A12" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
-      <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
     </row>
     <row r="13" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A13" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
     </row>
     <row r="14" spans="1:6" ht="17.100000000000001" customHeight="1">
       <c r="A14" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
     </row>
     <row r="16" spans="1:6" ht="15.6">
       <c r="A16" s="9" t="s">
